--- a/SID/SID V2 Method Back Testing.xlsx
+++ b/SID/SID V2 Method Back Testing.xlsx
@@ -25448,7 +25448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -25926,26 +25926,52 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
+          <t>v2-slope</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>104</v>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>67/37</t>
+        </is>
+      </c>
+      <c r="D27" s="47" t="n">
+        <v>0.7020000000000001</v>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>5218.45</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>v2-method</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B28" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>16/11</t>
         </is>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="D28" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>∞</t>
         </is>
       </c>
-      <c r="F27" s="17" t="n">
+      <c r="F28" s="8" t="n">
         <v>6089.33</v>
       </c>
     </row>

--- a/SID/SID V2 Method Back Testing.xlsx
+++ b/SID/SID V2 Method Back Testing.xlsx
@@ -258,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -344,22 +344,34 @@
     <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="10" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -391,9 +403,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -821,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y428"/>
+  <dimension ref="A1:Y429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -40086,6 +40095,75 @@
         </is>
       </c>
     </row>
+    <row r="429" ht="28" customHeight="1">
+      <c r="A429" s="29" t="inlineStr">
+        <is>
+          <t>SUBTOTAL ▼</t>
+        </is>
+      </c>
+      <c r="B429" s="29">
+        <f>SUBTOTAL(3,B4:B428)&amp;" trades"</f>
+        <v/>
+      </c>
+      <c r="C429" s="29" t="n"/>
+      <c r="D429" s="29" t="n"/>
+      <c r="E429" s="30">
+        <f>IFERROR(SUBTOTAL(1,E4:E428),0)</f>
+        <v/>
+      </c>
+      <c r="F429" s="30">
+        <f>IFERROR(SUBTOTAL(1,F4:F428),0)</f>
+        <v/>
+      </c>
+      <c r="G429" s="29" t="n"/>
+      <c r="H429" s="30">
+        <f>IFERROR(SUBTOTAL(1,H4:H428),0)</f>
+        <v/>
+      </c>
+      <c r="I429" s="29" t="n"/>
+      <c r="J429" s="29" t="n"/>
+      <c r="K429" s="29" t="n"/>
+      <c r="L429" s="31">
+        <f>SUBTOTAL(9,L4:L428)</f>
+        <v/>
+      </c>
+      <c r="M429" s="30">
+        <f>IFERROR(SUBTOTAL(1,M4:M428),0)</f>
+        <v/>
+      </c>
+      <c r="N429" s="31">
+        <f>SUBTOTAL(9,N4:N428)</f>
+        <v/>
+      </c>
+      <c r="O429" s="32">
+        <f>SUBTOTAL(9,O4:O428)</f>
+        <v/>
+      </c>
+      <c r="P429" s="31">
+        <f>SUBTOTAL(9,P4:P428)</f>
+        <v/>
+      </c>
+      <c r="Q429" s="33">
+        <f>IFERROR(SUBTOTAL(1,Q4:Q428),0)</f>
+        <v/>
+      </c>
+      <c r="R429" s="29" t="n"/>
+      <c r="S429" s="34">
+        <f>IFERROR(SUBTOTAL(1,S4:S428),0)</f>
+        <v/>
+      </c>
+      <c r="T429" s="34">
+        <f>IFERROR(SUBTOTAL(1,T4:T428),0)</f>
+        <v/>
+      </c>
+      <c r="U429" s="29" t="n"/>
+      <c r="V429" s="29" t="n"/>
+      <c r="W429" s="29" t="n"/>
+      <c r="X429" s="35">
+        <f>IFERROR(SUMPRODUCT(SUBTOTAL(3,OFFSET(X4,ROW(X4:X428)-ROW(X4),0))*(X4:X428="WIN"))/MAX(SUBTOTAL(3,X4:X428),1),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:Y428"/>
   <mergeCells count="2">
@@ -40173,7 +40251,7 @@
       <c r="D4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="29" t="n">
+      <c r="E4" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F4" s="12" t="n">
@@ -40223,7 +40301,7 @@
       <c r="D6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="36" t="n">
         <v>85.71428571428571</v>
       </c>
       <c r="F6" s="12" t="n">
@@ -40248,7 +40326,7 @@
       <c r="D7" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F7" s="27" t="n">
@@ -40273,7 +40351,7 @@
       <c r="D8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F8" s="12" t="n">
@@ -40298,7 +40376,7 @@
       <c r="D9" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F9" s="27" t="n">
@@ -40348,7 +40426,7 @@
       <c r="D11" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F11" s="27" t="n">
@@ -40373,7 +40451,7 @@
       <c r="D12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F12" s="12" t="n">
@@ -40423,7 +40501,7 @@
       <c r="D14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F14" s="12" t="n">
@@ -40448,7 +40526,7 @@
       <c r="D15" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F15" s="27" t="n">
@@ -40473,7 +40551,7 @@
       <c r="D16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="36" t="n">
         <v>80</v>
       </c>
       <c r="F16" s="12" t="n">
@@ -40498,7 +40576,7 @@
       <c r="D17" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="36" t="n">
         <v>71.42857142857143</v>
       </c>
       <c r="F17" s="27" t="n">
@@ -40523,7 +40601,7 @@
       <c r="D18" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F18" s="12" t="n">
@@ -40548,7 +40626,7 @@
       <c r="D19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F19" s="27" t="n">
@@ -40573,7 +40651,7 @@
       <c r="D20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="36" t="n">
         <v>80</v>
       </c>
       <c r="F20" s="12" t="n">
@@ -40598,7 +40676,7 @@
       <c r="D21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F21" s="27" t="n">
@@ -40623,7 +40701,7 @@
       <c r="D22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F22" s="12" t="n">
@@ -40648,7 +40726,7 @@
       <c r="D23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F23" s="27" t="n">
@@ -40673,7 +40751,7 @@
       <c r="D24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F24" s="12" t="n">
@@ -40698,7 +40776,7 @@
       <c r="D25" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="36" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="F25" s="27" t="n">
@@ -40723,7 +40801,7 @@
       <c r="D26" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="36" t="n">
         <v>75</v>
       </c>
       <c r="F26" s="12" t="n">
@@ -40748,7 +40826,7 @@
       <c r="D27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F27" s="27" t="n">
@@ -40773,7 +40851,7 @@
       <c r="D28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F28" s="12" t="n">
@@ -40823,7 +40901,7 @@
       <c r="D30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F30" s="12" t="n">
@@ -40848,7 +40926,7 @@
       <c r="D31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F31" s="27" t="n">
@@ -40873,7 +40951,7 @@
       <c r="D32" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="36" t="n">
         <v>75</v>
       </c>
       <c r="F32" s="12" t="n">
@@ -40898,7 +40976,7 @@
       <c r="D33" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F33" s="27" t="n">
@@ -40923,7 +41001,7 @@
       <c r="D34" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F34" s="12" t="n">
@@ -40948,7 +41026,7 @@
       <c r="D35" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="36" t="n">
         <v>75</v>
       </c>
       <c r="F35" s="27" t="n">
@@ -40998,7 +41076,7 @@
       <c r="D37" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="36" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="F37" s="27" t="n">
@@ -41023,7 +41101,7 @@
       <c r="D38" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F38" s="12" t="n">
@@ -41048,7 +41126,7 @@
       <c r="D39" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="36" t="n">
         <v>80</v>
       </c>
       <c r="F39" s="27" t="n">
@@ -41073,7 +41151,7 @@
       <c r="D40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F40" s="12" t="n">
@@ -41123,7 +41201,7 @@
       <c r="D42" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="36" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="F42" s="12" t="n">
@@ -41173,7 +41251,7 @@
       <c r="D44" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="36" t="n">
         <v>75</v>
       </c>
       <c r="F44" s="12" t="n">
@@ -41198,7 +41276,7 @@
       <c r="D45" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F45" s="27" t="n">
@@ -41223,7 +41301,7 @@
       <c r="D46" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="36" t="n">
         <v>75</v>
       </c>
       <c r="F46" s="12" t="n">
@@ -41273,7 +41351,7 @@
       <c r="D48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F48" s="12" t="n">
@@ -41298,7 +41376,7 @@
       <c r="D49" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F49" s="27" t="n">
@@ -41323,7 +41401,7 @@
       <c r="D50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F50" s="12" t="n">
@@ -41373,7 +41451,7 @@
       <c r="D52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F52" s="12" t="n">
@@ -41398,7 +41476,7 @@
       <c r="D53" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F53" s="27" t="n">
@@ -41423,7 +41501,7 @@
       <c r="D54" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="36" t="n">
         <v>75</v>
       </c>
       <c r="F54" s="12" t="n">
@@ -41448,7 +41526,7 @@
       <c r="D55" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E55" s="29" t="n">
+      <c r="E55" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F55" s="27" t="n">
@@ -41473,7 +41551,7 @@
       <c r="D56" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="29" t="n">
+      <c r="E56" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F56" s="12" t="n">
@@ -41498,7 +41576,7 @@
       <c r="D57" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E57" s="29" t="n">
+      <c r="E57" s="36" t="n">
         <v>75</v>
       </c>
       <c r="F57" s="27" t="n">
@@ -41598,7 +41676,7 @@
       <c r="D61" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E61" s="29" t="n">
+      <c r="E61" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F61" s="27" t="n">
@@ -41623,7 +41701,7 @@
       <c r="D62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E62" s="29" t="n">
+      <c r="E62" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F62" s="12" t="n">
@@ -41648,7 +41726,7 @@
       <c r="D63" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="29" t="n">
+      <c r="E63" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F63" s="27" t="n">
@@ -41698,7 +41776,7 @@
       <c r="D65" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E65" s="29" t="n">
+      <c r="E65" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F65" s="27" t="n">
@@ -41748,7 +41826,7 @@
       <c r="D67" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="29" t="n">
+      <c r="E67" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F67" s="27" t="n">
@@ -41773,7 +41851,7 @@
       <c r="D68" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E68" s="29" t="n">
+      <c r="E68" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F68" s="12" t="n">
@@ -41798,7 +41876,7 @@
       <c r="D69" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E69" s="29" t="n">
+      <c r="E69" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F69" s="27" t="n">
@@ -41823,7 +41901,7 @@
       <c r="D70" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E70" s="29" t="n">
+      <c r="E70" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F70" s="12" t="n">
@@ -41848,7 +41926,7 @@
       <c r="D71" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E71" s="29" t="n">
+      <c r="E71" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F71" s="27" t="n">
@@ -41873,7 +41951,7 @@
       <c r="D72" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E72" s="29" t="n">
+      <c r="E72" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F72" s="12" t="n">
@@ -41898,7 +41976,7 @@
       <c r="D73" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E73" s="29" t="n">
+      <c r="E73" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F73" s="27" t="n">
@@ -41923,7 +42001,7 @@
       <c r="D74" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E74" s="29" t="n">
+      <c r="E74" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F74" s="12" t="n">
@@ -41973,7 +42051,7 @@
       <c r="D76" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E76" s="29" t="n">
+      <c r="E76" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F76" s="12" t="n">
@@ -42023,7 +42101,7 @@
       <c r="D78" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E78" s="30" t="n">
+      <c r="E78" s="37" t="n">
         <v>25</v>
       </c>
       <c r="F78" s="12" t="n">
@@ -42048,7 +42126,7 @@
       <c r="D79" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E79" s="29" t="n">
+      <c r="E79" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F79" s="27" t="n">
@@ -42073,7 +42151,7 @@
       <c r="D80" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E80" s="29" t="n">
+      <c r="E80" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F80" s="12" t="n">
@@ -42123,7 +42201,7 @@
       <c r="D82" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E82" s="29" t="n">
+      <c r="E82" s="36" t="n">
         <v>100</v>
       </c>
       <c r="F82" s="12" t="n">
@@ -42198,7 +42276,7 @@
       <c r="D85" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E85" s="29" t="n">
+      <c r="E85" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F85" s="23" t="n">
@@ -42223,7 +42301,7 @@
       <c r="D86" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E86" s="30" t="n">
+      <c r="E86" s="37" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="F86" s="28" t="n">
@@ -42248,7 +42326,7 @@
       <c r="D87" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E87" s="30" t="n">
+      <c r="E87" s="37" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="F87" s="23" t="n">
@@ -42273,7 +42351,7 @@
       <c r="D88" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E88" s="29" t="n">
+      <c r="E88" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F88" s="28" t="n">
@@ -42348,7 +42426,7 @@
       <c r="D91" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E91" s="29" t="n">
+      <c r="E91" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F91" s="23" t="n">
@@ -42373,7 +42451,7 @@
       <c r="D92" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E92" s="30" t="n">
+      <c r="E92" s="37" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="28" t="n">
@@ -42398,7 +42476,7 @@
       <c r="D93" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E93" s="30" t="n">
+      <c r="E93" s="37" t="n">
         <v>0</v>
       </c>
       <c r="F93" s="23" t="n">
@@ -42423,7 +42501,7 @@
       <c r="D94" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E94" s="30" t="n">
+      <c r="E94" s="37" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="28" t="n">
@@ -42448,7 +42526,7 @@
       <c r="D95" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E95" s="30" t="n">
+      <c r="E95" s="37" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="23" t="n">
@@ -42498,7 +42576,7 @@
       <c r="D97" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E97" s="29" t="n">
+      <c r="E97" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F97" s="23" t="n">
@@ -42523,7 +42601,7 @@
       <c r="D98" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E98" s="29" t="n">
+      <c r="E98" s="36" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F98" s="28" t="n">
@@ -42573,7 +42651,7 @@
       <c r="D100" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E100" s="30" t="n">
+      <c r="E100" s="37" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="F100" s="28" t="n">
@@ -42598,7 +42676,7 @@
       <c r="D101" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E101" s="30" t="n">
+      <c r="E101" s="37" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="F101" s="23" t="n">
@@ -42623,7 +42701,7 @@
       <c r="D102" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E102" s="30" t="n">
+      <c r="E102" s="37" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="F102" s="28" t="n">
@@ -42648,7 +42726,7 @@
       <c r="D103" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="30" t="n">
+      <c r="E103" s="37" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="23" t="n">
@@ -42673,7 +42751,7 @@
       <c r="D104" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E104" s="30" t="n">
+      <c r="E104" s="37" t="n">
         <v>0</v>
       </c>
       <c r="F104" s="28" t="n">
@@ -42698,7 +42776,7 @@
       <c r="D105" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="E105" s="30" t="n">
+      <c r="E105" s="37" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="F105" s="23" t="n">
@@ -42748,7 +42826,7 @@
       <c r="D107" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E107" s="30" t="n">
+      <c r="E107" s="37" t="n">
         <v>0</v>
       </c>
       <c r="F107" s="23" t="n">
@@ -42773,7 +42851,7 @@
       <c r="D108" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E108" s="30" t="n">
+      <c r="E108" s="37" t="n">
         <v>16.66666666666666</v>
       </c>
       <c r="F108" s="28" t="n">
@@ -42798,7 +42876,7 @@
       <c r="D109" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E109" s="30" t="n">
+      <c r="E109" s="37" t="n">
         <v>16.66666666666666</v>
       </c>
       <c r="F109" s="23" t="n">
@@ -42823,7 +42901,7 @@
       <c r="D110" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E110" s="30" t="n">
+      <c r="E110" s="37" t="n">
         <v>16.66666666666666</v>
       </c>
       <c r="F110" s="28" t="n">
@@ -42834,32 +42912,32 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="31" t="inlineStr">
+      <c r="A111" s="29" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B111" s="32">
+      <c r="B111" s="38">
         <f>SUM(B4:B110)</f>
         <v/>
       </c>
-      <c r="C111" s="32">
+      <c r="C111" s="38">
         <f>SUM(C4:C110)</f>
         <v/>
       </c>
-      <c r="D111" s="32">
+      <c r="D111" s="38">
         <f>SUM(D4:D110)</f>
         <v/>
       </c>
-      <c r="E111" s="33">
+      <c r="E111" s="34">
         <f>C111/B111*100</f>
         <v/>
       </c>
-      <c r="F111" s="34">
+      <c r="F111" s="31">
         <f>SUM(F4:F110)</f>
         <v/>
       </c>
-      <c r="G111" s="33">
+      <c r="G111" s="34">
         <f>AVERAGE(G4:G110)</f>
         <v/>
       </c>
@@ -42930,288 +43008,288 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>Total trades</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n">
+      <c r="B5" s="40" t="n">
         <v>553</v>
       </c>
-      <c r="C5" s="36" t="n">
+      <c r="C5" s="40" t="n">
         <v>425</v>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="40" t="inlineStr">
         <is>
           <t>-128</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="40" t="inlineStr">
         <is>
           <t>V2 = stricter, fewer trades</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="B6" s="38" t="n">
+      <c r="B6" s="42" t="n">
         <v>313</v>
       </c>
-      <c r="C6" s="38" t="n">
+      <c r="C6" s="42" t="n">
         <v>275</v>
       </c>
-      <c r="D6" s="38" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>-38</t>
         </is>
       </c>
-      <c r="E6" s="38" t="inlineStr"/>
+      <c r="E6" s="42" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="40" t="n">
         <v>240</v>
       </c>
-      <c r="C7" s="36" t="n">
+      <c r="C7" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="D7" s="40" t="inlineStr">
         <is>
           <t>-90</t>
         </is>
       </c>
-      <c r="E7" s="36" t="inlineStr"/>
+      <c r="E7" s="40" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>Win Rate (%)</t>
         </is>
       </c>
-      <c r="B8" s="38" t="n">
+      <c r="B8" s="42" t="n">
         <v>56.6</v>
       </c>
-      <c r="C8" s="39" t="n">
+      <c r="C8" s="43" t="n">
         <v>64.7</v>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>+8.1pp</t>
         </is>
       </c>
-      <c r="E8" s="38" t="inlineStr">
+      <c r="E8" s="42" t="inlineStr">
         <is>
           <t>Community claim band: 65-75%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>Profit Factor</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
+      <c r="B9" s="40" t="n">
         <v>1.49</v>
       </c>
-      <c r="C9" s="36" t="n">
+      <c r="C9" s="40" t="n">
         <v>2.19</v>
       </c>
-      <c r="D9" s="36" t="inlineStr">
+      <c r="D9" s="40" t="inlineStr">
         <is>
           <t>+0.70</t>
         </is>
       </c>
-      <c r="E9" s="36" t="inlineStr">
+      <c r="E9" s="40" t="inlineStr">
         <is>
           <t>Higher = wins outweigh losses more</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>Starting balance</t>
         </is>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>$10,000</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="42" t="inlineStr">
         <is>
           <t>$10,000</t>
         </is>
       </c>
-      <c r="D10" s="38" t="inlineStr"/>
-      <c r="E10" s="38" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr"/>
+      <c r="E10" s="42" t="inlineStr">
         <is>
           <t>Both start at same balance</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>Final balance</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>$25,856.46</t>
         </is>
       </c>
-      <c r="C11" s="39" t="inlineStr">
+      <c r="C11" s="43" t="inlineStr">
         <is>
           <t>$43,327.80</t>
         </is>
       </c>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="D11" s="40" t="inlineStr">
         <is>
           <t>$+17,471.34</t>
         </is>
       </c>
-      <c r="E11" s="36" t="inlineStr">
+      <c r="E11" s="40" t="inlineStr">
         <is>
           <t>After all trades, compounded</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>Total return (%)</t>
         </is>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="42" t="inlineStr">
         <is>
           <t>158.56%</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="42" t="inlineStr">
         <is>
           <t>333.28%</t>
         </is>
       </c>
-      <c r="D12" s="38" t="inlineStr">
+      <c r="D12" s="42" t="inlineStr">
         <is>
           <t>+174.7pp</t>
         </is>
       </c>
-      <c r="E12" s="38" t="inlineStr"/>
+      <c r="E12" s="42" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>CAGR (%)</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>21.08%</t>
         </is>
       </c>
-      <c r="C13" s="39" t="inlineStr">
+      <c r="C13" s="43" t="inlineStr">
         <is>
           <t>34.67%</t>
         </is>
       </c>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="D13" s="40" t="inlineStr">
         <is>
           <t>+13.6pp</t>
         </is>
       </c>
-      <c r="E13" s="36" t="inlineStr">
+      <c r="E13" s="40" t="inlineStr">
         <is>
           <t>Compounded annual growth rate</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>17.02%</t>
         </is>
       </c>
-      <c r="C14" s="39" t="inlineStr">
+      <c r="C14" s="43" t="inlineStr">
         <is>
           <t>7.95%</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D14" s="42" t="inlineStr">
         <is>
           <t>-9.1pp</t>
         </is>
       </c>
-      <c r="E14" s="38" t="inlineStr">
+      <c r="E14" s="42" t="inlineStr">
         <is>
           <t>Peak-to-trough decline</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>Avg win ($)</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>$154.14</t>
         </is>
       </c>
-      <c r="C15" s="36" t="inlineStr">
+      <c r="C15" s="40" t="inlineStr">
         <is>
           <t>$222.72</t>
         </is>
       </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="D15" s="40" t="inlineStr">
         <is>
           <t>$+68.58</t>
         </is>
       </c>
-      <c r="E15" s="36" t="inlineStr">
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>Scales with account growth</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="41" t="inlineStr">
         <is>
           <t>Avg loss ($)</t>
         </is>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>$-134.96</t>
         </is>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C16" s="42" t="inlineStr">
         <is>
           <t>$-186.14</t>
         </is>
       </c>
-      <c r="D16" s="38" t="inlineStr">
+      <c r="D16" s="42" t="inlineStr">
         <is>
           <t>$-51.18</t>
         </is>
       </c>
-      <c r="E16" s="38" t="inlineStr">
+      <c r="E16" s="42" t="inlineStr">
         <is>
           <t>Scales with account growth</t>
         </is>
@@ -43251,39 +43329,39 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="40" t="inlineStr">
+      <c r="A3" s="44" t="inlineStr">
         <is>
           <t>Year-end account balance (after each calendar year of trades)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="45" t="inlineStr">
         <is>
           <t>Start Balance</t>
         </is>
       </c>
-      <c r="C5" s="41" t="inlineStr">
+      <c r="C5" s="45" t="inlineStr">
         <is>
           <t>End Balance</t>
         </is>
       </c>
-      <c r="D5" s="41" t="inlineStr">
+      <c r="D5" s="45" t="inlineStr">
         <is>
           <t>$ Gain</t>
         </is>
       </c>
-      <c r="E5" s="41" t="inlineStr">
+      <c r="E5" s="45" t="inlineStr">
         <is>
           <t>% Gain</t>
         </is>
       </c>
-      <c r="F5" s="41" t="inlineStr">
+      <c r="F5" s="45" t="inlineStr">
         <is>
           <t>Trades</t>
         </is>
@@ -43293,16 +43371,16 @@
       <c r="A6" s="4" t="n">
         <v>2021</v>
       </c>
-      <c r="B6" s="42" t="n">
+      <c r="B6" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="C6" s="42" t="n">
+      <c r="C6" s="46" t="n">
         <v>12946.2</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>2946.200000000001</v>
       </c>
-      <c r="E6" s="43" t="n">
+      <c r="E6" s="47" t="n">
         <v>0.29462</v>
       </c>
       <c r="F6" s="4" t="n">
@@ -43313,16 +43391,16 @@
       <c r="A7" s="18" t="n">
         <v>2022</v>
       </c>
-      <c r="B7" s="44" t="n">
+      <c r="B7" s="48" t="n">
         <v>12946.2</v>
       </c>
-      <c r="C7" s="44" t="n">
+      <c r="C7" s="48" t="n">
         <v>14885.06</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>1938.859999999999</v>
       </c>
-      <c r="E7" s="45" t="n">
+      <c r="E7" s="49" t="n">
         <v>0.1497628647788539</v>
       </c>
       <c r="F7" s="18" t="n">
@@ -43333,16 +43411,16 @@
       <c r="A8" s="4" t="n">
         <v>2023</v>
       </c>
-      <c r="B8" s="42" t="n">
+      <c r="B8" s="46" t="n">
         <v>14885.06</v>
       </c>
-      <c r="C8" s="42" t="n">
+      <c r="C8" s="46" t="n">
         <v>19294.07</v>
       </c>
       <c r="D8" s="12" t="n">
         <v>4409.01</v>
       </c>
-      <c r="E8" s="43" t="n">
+      <c r="E8" s="47" t="n">
         <v>0.2962037102974392</v>
       </c>
       <c r="F8" s="4" t="n">
@@ -43353,16 +43431,16 @@
       <c r="A9" s="18" t="n">
         <v>2024</v>
       </c>
-      <c r="B9" s="44" t="n">
+      <c r="B9" s="48" t="n">
         <v>19294.07</v>
       </c>
-      <c r="C9" s="44" t="n">
+      <c r="C9" s="48" t="n">
         <v>26145.63</v>
       </c>
       <c r="D9" s="27" t="n">
         <v>6851.560000000001</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="49" t="n">
         <v>0.3551122184173687</v>
       </c>
       <c r="F9" s="18" t="n">
@@ -43373,16 +43451,16 @@
       <c r="A10" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="B10" s="42" t="n">
+      <c r="B10" s="46" t="n">
         <v>26145.63</v>
       </c>
-      <c r="C10" s="42" t="n">
+      <c r="C10" s="46" t="n">
         <v>35075.97</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>8930.34</v>
       </c>
-      <c r="E10" s="43" t="n">
+      <c r="E10" s="47" t="n">
         <v>0.3415614770039965</v>
       </c>
       <c r="F10" s="4" t="n">
@@ -43393,16 +43471,16 @@
       <c r="A11" s="18" t="n">
         <v>2026</v>
       </c>
-      <c r="B11" s="44" t="n">
+      <c r="B11" s="48" t="n">
         <v>35075.97</v>
       </c>
-      <c r="C11" s="44" t="n">
+      <c r="C11" s="48" t="n">
         <v>43327.8</v>
       </c>
       <c r="D11" s="27" t="n">
         <v>8251.830000000002</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="49" t="n">
         <v>0.2352559316249843</v>
       </c>
       <c r="F11" s="18" t="n">
@@ -43410,131 +43488,131 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="46" t="n">
+      <c r="B12" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="C12" s="46" t="n">
+      <c r="C12" s="30" t="n">
         <v>43327.8</v>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D12" s="31" t="n">
         <v>33327.8</v>
       </c>
-      <c r="E12" s="47" t="n">
+      <c r="E12" s="50" t="n">
         <v>3.33278</v>
       </c>
-      <c r="F12" s="32" t="n">
+      <c r="F12" s="38" t="n">
         <v>425</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="44" t="inlineStr">
         <is>
           <t>Projection — using V2 CAGR 34.7% as growth rate</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="inlineStr">
+      <c r="A17" s="45" t="inlineStr">
         <is>
           <t>Starting Capital</t>
         </is>
       </c>
-      <c r="B17" s="41" t="inlineStr">
+      <c r="B17" s="45" t="inlineStr">
         <is>
           <t>After 1 Year</t>
         </is>
       </c>
-      <c r="C17" s="41" t="inlineStr">
+      <c r="C17" s="45" t="inlineStr">
         <is>
           <t>After 2 Years</t>
         </is>
       </c>
-      <c r="D17" s="41" t="inlineStr">
+      <c r="D17" s="45" t="inlineStr">
         <is>
           <t>After 3 Years</t>
         </is>
       </c>
-      <c r="E17" s="41" t="inlineStr">
+      <c r="E17" s="45" t="inlineStr">
         <is>
           <t>After 5 Years</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="n">
+      <c r="A18" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="B18" s="49" t="n">
+      <c r="B18" s="52" t="n">
         <v>13467</v>
       </c>
-      <c r="C18" s="49" t="n">
+      <c r="C18" s="52" t="n">
         <v>18136.0089</v>
       </c>
-      <c r="D18" s="49" t="n">
+      <c r="D18" s="52" t="n">
         <v>24423.76318563</v>
       </c>
-      <c r="E18" s="49" t="n">
+      <c r="E18" s="52" t="n">
         <v>44294.9586506078</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="50" t="n">
+      <c r="A19" s="53" t="n">
         <v>20000</v>
       </c>
-      <c r="B19" s="51" t="n">
+      <c r="B19" s="54" t="n">
         <v>26934</v>
       </c>
-      <c r="C19" s="51" t="n">
+      <c r="C19" s="54" t="n">
         <v>36272.0178</v>
       </c>
-      <c r="D19" s="51" t="n">
+      <c r="D19" s="54" t="n">
         <v>48847.52637126</v>
       </c>
-      <c r="E19" s="51" t="n">
+      <c r="E19" s="54" t="n">
         <v>88589.91730121561</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="n">
+      <c r="A20" s="51" t="n">
         <v>50000</v>
       </c>
-      <c r="B20" s="49" t="n">
+      <c r="B20" s="52" t="n">
         <v>67335</v>
       </c>
-      <c r="C20" s="49" t="n">
+      <c r="C20" s="52" t="n">
         <v>90680.0445</v>
       </c>
-      <c r="D20" s="49" t="n">
+      <c r="D20" s="52" t="n">
         <v>122118.81592815</v>
       </c>
-      <c r="E20" s="49" t="n">
+      <c r="E20" s="52" t="n">
         <v>221474.793253039</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="50" t="n">
+      <c r="A21" s="53" t="n">
         <v>100000</v>
       </c>
-      <c r="B21" s="51" t="n">
+      <c r="B21" s="54" t="n">
         <v>134670</v>
       </c>
-      <c r="C21" s="51" t="n">
+      <c r="C21" s="54" t="n">
         <v>181360.089</v>
       </c>
-      <c r="D21" s="51" t="n">
+      <c r="D21" s="54" t="n">
         <v>244237.6318563</v>
       </c>
-      <c r="E21" s="51" t="n">
+      <c r="E21" s="54" t="n">
         <v>442949.5865060781</v>
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="52" t="inlineStr">
+      <c r="A23" s="55" t="inlineStr">
         <is>
           <t>Reality check: live WR will likely be 5-10pp lower than 69.5%. Use 50-70% of these projections as realistic outcomes. Drawdowns of 10-15% are expected even on winning strategies.</t>
         </is>
@@ -43573,504 +43651,504 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="56" t="inlineStr">
         <is>
           <t>Stage 1 — ARM (signal day)</t>
         </is>
       </c>
-      <c r="B3" s="54" t="inlineStr"/>
-      <c r="C3" s="54" t="inlineStr"/>
+      <c r="B3" s="57" t="inlineStr"/>
+      <c r="C3" s="57" t="inlineStr"/>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="55" t="inlineStr">
+      <c r="A4" s="58" t="inlineStr">
         <is>
           <t>Daily RSI(14) oversold (long)</t>
         </is>
       </c>
-      <c r="B4" s="55" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr">
         <is>
           <t>&lt; 30</t>
         </is>
       </c>
-      <c r="C4" s="55" t="inlineStr">
+      <c r="C4" s="58" t="inlineStr">
         <is>
           <t>Triggers long arm</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="56" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>Daily RSI(14) overbought (short)</t>
         </is>
       </c>
-      <c r="B5" s="56" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>&gt; 70 (V2 uses 70 not 75)</t>
         </is>
       </c>
-      <c r="C5" s="56" t="inlineStr">
+      <c r="C5" s="59" t="inlineStr">
         <is>
           <t>Triggers short arm. V1 used 75.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>Daily RSI(3) confirmation</t>
         </is>
       </c>
-      <c r="B6" s="55" t="inlineStr">
+      <c r="B6" s="58" t="inlineStr">
         <is>
           <t>Must be in extreme zone</t>
         </is>
       </c>
-      <c r="C6" s="55" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>Rebound-zone confirmation, carried from V1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="56" t="inlineStr">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>Weekly trend filter (50/200 SMA)</t>
         </is>
       </c>
-      <c r="B7" s="56" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>Long: 50SMA&gt;200SMA; Short: 50SMA&lt;200SMA</t>
         </is>
       </c>
-      <c r="C7" s="56" t="inlineStr">
+      <c r="C7" s="59" t="inlineStr">
         <is>
           <t>Retained from V1 for safety</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A8" s="58" t="inlineStr">
         <is>
           <t>Earnings blackout</t>
         </is>
       </c>
-      <c r="B8" s="55" t="inlineStr">
+      <c r="B8" s="58" t="inlineStr">
         <is>
           <t>14 days pre-earnings</t>
         </is>
       </c>
-      <c r="C8" s="55" t="inlineStr">
+      <c r="C8" s="58" t="inlineStr">
         <is>
           <t>Skip new arms inside this window</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="53" t="inlineStr">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>Stage 2 — TRIGGER (entry day)</t>
         </is>
       </c>
-      <c r="B9" s="54" t="inlineStr"/>
-      <c r="C9" s="54" t="inlineStr"/>
+      <c r="B9" s="57" t="inlineStr"/>
+      <c r="C9" s="57" t="inlineStr"/>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>Daily RSI direction</t>
         </is>
       </c>
-      <c r="B10" s="55" t="inlineStr">
+      <c r="B10" s="58" t="inlineStr">
         <is>
           <t>Pointing in trade direction</t>
         </is>
       </c>
-      <c r="C10" s="55" t="inlineStr">
+      <c r="C10" s="58" t="inlineStr">
         <is>
           <t>Long: rising. Short: falling.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="56" t="inlineStr">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>Daily MACD direction</t>
         </is>
       </c>
-      <c r="B11" s="56" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t>Pointing in trade direction</t>
         </is>
       </c>
-      <c r="C11" s="56" t="inlineStr">
+      <c r="C11" s="59" t="inlineStr">
         <is>
           <t>Long: rising. Short: falling.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="57" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>Weekly RSI direction</t>
         </is>
       </c>
-      <c r="B12" s="57" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>Same direction as trade (v2-weekly-or: this OR weekly MACD)</t>
         </is>
       </c>
-      <c r="C12" s="57" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>NEW IN V2</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="57" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>Weekly MACD direction</t>
         </is>
       </c>
-      <c r="B13" s="57" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>Same direction as trade (either weekly indicator passes)</t>
         </is>
       </c>
-      <c r="C13" s="57" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>NEW IN V2</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="57" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>No-go zone (long)</t>
         </is>
       </c>
-      <c r="B14" s="57" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>Entry RSI must be &lt; 45</t>
         </is>
       </c>
-      <c r="C14" s="57" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>INSTRUCTOR S2_Ep3: "too close to RSI 50"</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="57" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>No-go zone (short)</t>
         </is>
       </c>
-      <c r="B15" s="57" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>Entry RSI must be &gt; 55</t>
         </is>
       </c>
-      <c r="C15" s="57" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>INSTRUCTOR S2_Ep3: "too close to RSI 50"</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="55" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>Pattern bonus (W/M/H&amp;S)</t>
         </is>
       </c>
-      <c r="B16" s="55" t="inlineStr">
+      <c r="B16" s="58" t="inlineStr">
         <is>
           <t>Bonus, NOT required</t>
         </is>
       </c>
-      <c r="C16" s="55" t="inlineStr">
+      <c r="C16" s="58" t="inlineStr">
         <is>
           <t>Deferred to V2.1 — see Pine divergence indicator</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="56" t="inlineStr">
+      <c r="A17" s="59" t="inlineStr">
         <is>
           <t>Sticky arm window</t>
         </is>
       </c>
-      <c r="B17" s="56" t="inlineStr">
+      <c r="B17" s="59" t="inlineStr">
         <is>
           <t>3 trading days</t>
         </is>
       </c>
-      <c r="C17" s="56" t="inlineStr">
+      <c r="C17" s="59" t="inlineStr">
         <is>
           <t>If trigger not met within 3 days, arm cancels</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="53" t="inlineStr">
+      <c r="A18" s="56" t="inlineStr">
         <is>
           <t>Stage 3 — EXIT</t>
         </is>
       </c>
-      <c r="B18" s="54" t="inlineStr"/>
-      <c r="C18" s="54" t="inlineStr"/>
+      <c r="B18" s="57" t="inlineStr"/>
+      <c r="C18" s="57" t="inlineStr"/>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="56" t="inlineStr">
+      <c r="A19" s="59" t="inlineStr">
         <is>
           <t>Take profit</t>
         </is>
       </c>
-      <c r="B19" s="56" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>Daily RSI(14) reaches 50</t>
         </is>
       </c>
-      <c r="C19" s="56" t="inlineStr">
+      <c r="C19" s="59" t="inlineStr">
         <is>
           <t>Single full exit. V1-compatible.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="55" t="inlineStr">
+      <c r="A20" s="58" t="inlineStr">
         <is>
           <t>Stop loss (long)</t>
         </is>
       </c>
-      <c r="B20" s="55" t="inlineStr">
+      <c r="B20" s="58" t="inlineStr">
         <is>
           <t>Lowest low signal→entry, FLOOR to whole $</t>
         </is>
       </c>
-      <c r="C20" s="55" t="inlineStr">
+      <c r="C20" s="58" t="inlineStr">
         <is>
           <t>Hard stop, never moved</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="56" t="inlineStr">
+      <c r="A21" s="59" t="inlineStr">
         <is>
           <t>Stop loss (short)</t>
         </is>
       </c>
-      <c r="B21" s="56" t="inlineStr">
+      <c r="B21" s="59" t="inlineStr">
         <is>
           <t>Highest high signal→entry, CEIL to whole $</t>
         </is>
       </c>
-      <c r="C21" s="56" t="inlineStr">
+      <c r="C21" s="59" t="inlineStr">
         <is>
           <t>Hard stop, never moved</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="53" t="inlineStr">
+      <c r="A22" s="56" t="inlineStr">
         <is>
           <t>Risk &amp; Position Sizing (INSTRUCTOR METHODOLOGY)</t>
         </is>
       </c>
-      <c r="B22" s="54" t="inlineStr"/>
-      <c r="C22" s="54" t="inlineStr"/>
+      <c r="B22" s="57" t="inlineStr"/>
+      <c r="C22" s="57" t="inlineStr"/>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="56" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>Account balance</t>
         </is>
       </c>
-      <c r="B23" s="56" t="inlineStr">
+      <c r="B23" s="59" t="inlineStr">
         <is>
           <t>$10,000 (this backtest)</t>
         </is>
       </c>
-      <c r="C23" s="56" t="inlineStr">
+      <c r="C23" s="59" t="inlineStr">
         <is>
           <t>Scales with growth — each trade uses current balance</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="A24" s="58" t="inlineStr">
         <is>
           <t>Risk per trade</t>
         </is>
       </c>
-      <c r="B24" s="55" t="inlineStr">
+      <c r="B24" s="58" t="inlineStr">
         <is>
           <t>1% (instructor default)</t>
         </is>
       </c>
-      <c r="C24" s="55" t="inlineStr">
+      <c r="C24" s="58" t="inlineStr">
         <is>
           <t>S3_Ep4: "typically between 0.5% and 2%. We will use 1%."</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="56" t="inlineStr">
+      <c r="A25" s="59" t="inlineStr">
         <is>
           <t>Risk $ formula</t>
         </is>
       </c>
-      <c r="B25" s="56" t="inlineStr">
+      <c r="B25" s="59" t="inlineStr">
         <is>
           <t>Account × Risk %</t>
         </is>
       </c>
-      <c r="C25" s="56" t="inlineStr">
+      <c r="C25" s="59" t="inlineStr">
         <is>
           <t>1% of $10K = $100 risk</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="55" t="inlineStr">
+      <c r="A26" s="58" t="inlineStr">
         <is>
           <t>Risk per share</t>
         </is>
       </c>
-      <c r="B26" s="55" t="inlineStr">
+      <c r="B26" s="58" t="inlineStr">
         <is>
           <t>|Entry − Stop|</t>
         </is>
       </c>
-      <c r="C26" s="55" t="inlineStr">
+      <c r="C26" s="58" t="inlineStr">
         <is>
           <t>Difference in dollars per share</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="56" t="inlineStr">
+      <c r="A27" s="59" t="inlineStr">
         <is>
           <t>Shares (sized)</t>
         </is>
       </c>
-      <c r="B27" s="56" t="inlineStr">
+      <c r="B27" s="59" t="inlineStr">
         <is>
           <t>ROUNDDOWN(Risk $ / Risk per share)</t>
         </is>
       </c>
-      <c r="C27" s="56" t="inlineStr">
+      <c r="C27" s="59" t="inlineStr">
         <is>
           <t>Whole share count, no fractions</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="55" t="inlineStr">
+      <c r="A28" s="58" t="inlineStr">
         <is>
           <t>Position size $</t>
         </is>
       </c>
-      <c r="B28" s="55" t="inlineStr">
+      <c r="B28" s="58" t="inlineStr">
         <is>
           <t>Shares × Entry price</t>
         </is>
       </c>
-      <c r="C28" s="55" t="inlineStr">
+      <c r="C28" s="58" t="inlineStr">
         <is>
           <t>Capital deployed for the position</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="56" t="inlineStr">
+      <c r="A29" s="59" t="inlineStr">
         <is>
           <t>Cash trading</t>
         </is>
       </c>
-      <c r="B29" s="56" t="inlineStr">
+      <c r="B29" s="59" t="inlineStr">
         <is>
           <t>No margin, position ≤ account</t>
         </is>
       </c>
-      <c r="C29" s="56" t="inlineStr">
+      <c r="C29" s="59" t="inlineStr">
         <is>
           <t>Instructor teaches cash only</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="55" t="inlineStr">
+      <c r="A30" s="58" t="inlineStr">
         <is>
           <t>Maximum risk per trade</t>
         </is>
       </c>
-      <c r="B30" s="55" t="inlineStr">
+      <c r="B30" s="58" t="inlineStr">
         <is>
           <t>2% (NEVER exceed)</t>
         </is>
       </c>
-      <c r="C30" s="55" t="inlineStr">
+      <c r="C30" s="58" t="inlineStr">
         <is>
           <t>S3_P3: "never go higher than 2%"</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="56" t="inlineStr">
+      <c r="A31" s="59" t="inlineStr">
         <is>
           <t>When to scale up</t>
         </is>
       </c>
-      <c r="B31" s="56" t="inlineStr">
+      <c r="B31" s="59" t="inlineStr">
         <is>
           <t>After 6-12 months live track record</t>
         </is>
       </c>
-      <c r="C31" s="56" t="inlineStr">
+      <c r="C31" s="59" t="inlineStr">
         <is>
           <t>Build confidence before adding risk</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="53" t="inlineStr">
+      <c r="A32" s="56" t="inlineStr">
         <is>
           <t>Architecture</t>
         </is>
       </c>
-      <c r="B32" s="54" t="inlineStr"/>
-      <c r="C32" s="54" t="inlineStr"/>
+      <c r="B32" s="57" t="inlineStr"/>
+      <c r="C32" s="57" t="inlineStr"/>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="56" t="inlineStr">
+      <c r="A33" s="59" t="inlineStr">
         <is>
           <t>SID_METHOD env var</t>
         </is>
       </c>
-      <c r="B33" s="56" t="inlineStr">
+      <c r="B33" s="59" t="inlineStr">
         <is>
           <t>Default 'v1'; set 'v2' to enable</t>
         </is>
       </c>
-      <c r="C33" s="56" t="inlineStr">
+      <c r="C33" s="59" t="inlineStr">
         <is>
           <t>Bot toggles between methods</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="55" t="inlineStr">
+      <c r="A34" s="58" t="inlineStr">
         <is>
           <t>V1 baseline tag</t>
         </is>
       </c>
-      <c r="B34" s="55" t="inlineStr">
+      <c r="B34" s="58" t="inlineStr">
         <is>
           <t>sid-v1-method-baseline (commit bdef9be)</t>
         </is>
       </c>
-      <c r="C34" s="55" t="inlineStr">
+      <c r="C34" s="58" t="inlineStr">
         <is>
           <t>Instant revert if V2 underperforms</t>
         </is>
@@ -44109,144 +44187,144 @@
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>AUTO = ticker in proven 80-ticker tier1 list (5y V1 backtest validated). HUMAN = high-vol / crypto / leveraged ETFs / re-added dropouts. Bot sends Telegram alert with proposed Entry / SL / TP for HUMAN trades.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="41" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="45" t="inlineStr">
         <is>
           <t>Trades</t>
         </is>
       </c>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="C4" s="45" t="inlineStr">
         <is>
           <t>Tickers</t>
         </is>
       </c>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D4" s="45" t="inlineStr">
         <is>
           <t>WR (%)</t>
         </is>
       </c>
-      <c r="E4" s="41" t="inlineStr">
+      <c r="E4" s="45" t="inlineStr">
         <is>
           <t>Net P&amp;L ($)</t>
         </is>
       </c>
-      <c r="F4" s="41" t="inlineStr">
+      <c r="F4" s="45" t="inlineStr">
         <is>
           <t>Avg P&amp;L per trade ($)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="62" t="inlineStr">
         <is>
           <t>AUTO (tier1 80)</t>
         </is>
       </c>
-      <c r="B5" s="60" t="n">
+      <c r="B5" s="63" t="n">
         <v>297</v>
       </c>
-      <c r="C5" s="60" t="n">
+      <c r="C5" s="63" t="n">
         <v>77</v>
       </c>
-      <c r="D5" s="61" t="n">
+      <c r="D5" s="64" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="E5" s="62" t="n">
+      <c r="E5" s="65" t="n">
         <v>31623.3</v>
       </c>
-      <c r="F5" s="62" t="n">
+      <c r="F5" s="65" t="n">
         <v>106.48</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="63" t="inlineStr">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>HUMAN (tier2 32)</t>
         </is>
       </c>
-      <c r="B6" s="64" t="n">
+      <c r="B6" s="67" t="n">
         <v>128</v>
       </c>
-      <c r="C6" s="64" t="n">
+      <c r="C6" s="67" t="n">
         <v>30</v>
       </c>
-      <c r="D6" s="65" t="n">
+      <c r="D6" s="68" t="n">
         <v>51.6</v>
       </c>
-      <c r="E6" s="66" t="n">
+      <c r="E6" s="69" t="n">
         <v>1704.5</v>
       </c>
-      <c r="F6" s="66" t="n">
+      <c r="F6" s="69" t="n">
         <v>13.32</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
+      <c r="B7" s="38" t="n">
         <v>425</v>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="38" t="n">
         <v>107</v>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="34" t="n">
         <v>64.7</v>
       </c>
-      <c r="E7" s="34" t="n">
+      <c r="E7" s="31" t="n">
         <v>33327.8</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F7" s="31" t="n">
         <v>78.42</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="44" t="inlineStr">
         <is>
           <t>HUMAN-tier tickers — trade count, WR, P&amp;L (rank by total trades)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="inlineStr">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B12" s="41" t="inlineStr">
+      <c r="B12" s="45" t="inlineStr">
         <is>
           <t>Trades</t>
         </is>
       </c>
-      <c r="C12" s="41" t="inlineStr">
+      <c r="C12" s="45" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="D12" s="41" t="inlineStr">
+      <c r="D12" s="45" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
       </c>
-      <c r="E12" s="41" t="inlineStr">
+      <c r="E12" s="45" t="inlineStr">
         <is>
           <t>WR (%)</t>
         </is>
       </c>
-      <c r="F12" s="41" t="inlineStr">
+      <c r="F12" s="45" t="inlineStr">
         <is>
           <t>Net P&amp;L ($)</t>
         </is>
